--- a/astro-site/public/dl/pack-appcc/13-checklist-higiene-personal.xlsx
+++ b/astro-site/public/dl/pack-appcc/13-checklist-higiene-personal.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Higiene Personal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Higiene Personal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -113,30 +113,30 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -496,15 +496,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -512,6 +513,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -519,9 +521,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -543,13 +543,19 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -557,7 +563,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -566,16 +581,17 @@
   <sheetPr>
     <tabColor rgb="0000BCD4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:C36"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="55"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -583,6 +599,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -864,6 +881,8 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -871,6 +890,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -889,7 +909,15 @@
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/13-checklist-higiene-personal.xlsx
+++ b/astro-site/public/dl/pack-appcc/13-checklist-higiene-personal.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Higiene Personal" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Higiene Personal'!$A$1:$C$41</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +77,37 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -88,8 +120,13 @@
         <bgColor rgb="002D2D2D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -111,11 +148,25 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,6 +183,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,16 +574,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Checklist de Higiene Personal</t>
         </is>
@@ -515,7 +591,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -523,47 +599,90 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Imprime y coloca en vestuario y entrada a cocina</t>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>▸ Imprímela en A4 vertical y cuélgala en el vestuario y en la puerta de acceso a la cocina.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Todo el personal debe cumplir ANTES de entrar a zona de manipulación</t>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>▸ Todo el personal debe cumplir estos puntos ANTES de entrar en la zona de manipulación.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ El encargado verifica semanalmente</t>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>▸ El encargado verifica semanalmente, marca las casillas y firma al pie. Archiva la hoja firmada.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>El carné oficial de manipulador ya no existe</t>
         </is>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>El carné oficial de manipulador de alimentos se suprimió en España con el RD 109/2010, que derogó el RD 202/2000. No hay carné, no hay caducidad y no hay que renovar nada en ninguna ventanilla. Lo que exige la norma vigente (Reg. (CE) 852/2004, Anexo II, Cap. XII) es que la EMPRESA garantice y pueda acreditar que sus manipuladores están formados y supervisados. Esa formación la registras en el BONUS-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Bajas por enfermedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>▸ Quien tenga vómitos, diarrea, fiebre, lesiones cutáneas infectadas o supuración no puede manipular alimentos. La vuelta al puesto se hace 48 horas después de que cesen los síntomas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>▸ El trabajador tiene la obligación de comunicarlo y la empresa la de recolocarlo o darle de baja: es responsabilidad compartida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -583,333 +702,401 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>NORMAS DE HIGIENE PERSONAL — Zona de Manipulación</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="5" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>NORMAS DE HIGIENE PERSONAL — Zona de manipulación</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Reg. (CE) 852/2004, Anexo II, Cap. VIII. Comprueba estos puntos ANTES de entrar a manipular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>INDUMENTARIA</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Uniforme limpio y exclusivo para trabajo</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="C5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Uniforme limpio y de uso exclusivo para el trabajo</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Gorro o cofia que cubra todo el cabello</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="7" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Calzado cerrado, antideslizante y limpio</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Sin joyas, relojes ni piercings visibles</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Delantal limpio (cambiar si se ensucia)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Sin joyas, relojes, pulseras ni piercings visibles</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Delantal limpio; cambiarlo en cuanto se ensucie</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>MANOS</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Uñas cortas, limpias, sin esmalte</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Lavado de manos al entrar a cocina</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="C12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Uñas cortas, limpias, sin esmalte ni uñas postizas</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Lavado de manos al entrar en la cocina</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Lavado de manos después de ir al baño</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Lavado de manos al cambiar de tarea</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Lavado de manos después de tocar basura</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Uso de guantes cuando sea necesario (heridas)</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Cubrir heridas con apósito azul impermeable</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>CONDUCTA</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>No comer, beber ni fumar en zona de trabajo</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>No toser ni estornudar sobre alimentos</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>No tocar cara, pelo ni nariz mientras se cocina</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Informar al encargado si se está enfermo (vómitos, diarrea, fiebre)</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>No trabajar con síntomas gastrointestinales</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>FORMACIÓN</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Carné/certificado de manipulador de alimentos vigente</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Formación APPCC básica recibida</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Conocimiento de alérgenos y protocolo</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33">
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Responsable verificación: _________________________    Fecha: ___/___/______</t>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Lavado de manos al cambiar de tarea o de alimento</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Lavado de manos después de tocar basura, cajas o dinero</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Guantes si hay heridas; cambiarlos al cambiar de tarea</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Heridas cubiertas con apósito azul impermeable</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>CONDUCTA Y SALUD</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>No comer, beber, mascar chicle ni fumar en la zona de trabajo</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>No toser ni estornudar sobre los alimentos</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>No tocarse cara, pelo ni nariz mientras se manipula comida</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Avisar al encargado ante vómitos, diarrea, fiebre o infección de la piel</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>No trabajar con síntomas gastrointestinales hasta 48 h después de que cesen</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Ropa de calle y ropa de trabajo separadas en la taquilla</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>FORMACIÓN Y REGISTRO</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="46" customHeight="1">
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Formación en higiene alimentaria acreditada por la empresa (Reg. (CE) 852/2004, Anexo II, Cap. XII; el carné oficial se suprimió con el RD 109/2010)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Formación específica en alérgenos y protocolo de actuación (ficha 14)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Formación básica en APPCC recibida y registrada</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Alta en el registro de formación del establecimiento (BONUS-01)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>☐</t>
         </is>
       </c>
     </row>
     <row r="34"/>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Imprimir y colocar en vestuario y puerta de acceso a cocina.</t>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Responsable de la verificación: ____________________________</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Fecha: ___/___/______      Firma: __________________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="24.5" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Imprime este cartel y cuélgalo en el vestuario y en la puerta de acceso a la cocina. El encargado lo verifica semanalmente y lo firma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36.7" customHeight="1">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>El carné oficial de manipulador de alimentos NO existe desde el RD 109/2010: lo que la inspección comprueba es que la EMPRESA acredite la formación en higiene de cada trabajador (Reg. (CE) 852/2004, Anexo II, Cap. XII). Registra esa formación en el BONUS-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36.7" customHeight="1">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="12.2" customHeight="1">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
